--- a/test/003_UT-画面遷移テスト/画面遷移テスト証跡.xlsx
+++ b/test/003_UT-画面遷移テスト/画面遷移テスト証跡.xlsx
@@ -17,6 +17,15 @@
     <sheet name="UT-FLOW-006" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="UT-FLOW-007" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="UT-FLOW-008" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="UT-FLOW-019" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="UT-FLOW-020" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="UT-FLOW-021" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="UT-FLOW-022" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="UT-FLOW-023" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="UT-FLOW-024" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="UT-FLOW-025" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="UT-FLOW-026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="UT-FLOW-027" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -333,6 +342,246 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -514,6 +763,36 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="5362575"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -57192,6 +57471,411 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-019　ログイン画面 UI 表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：ロゴ・代理店コード/ログインID/パスワード入力欄・ログインボタン・パスワードお忘れリンクの全表示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-020　A001 ダッシュボード 更改状況グラフ確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：今月更改28件完了/11.3%、翌月更改125件完了/38.5% のグラフ表示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-021　満期管理一覧 デフォルト表示確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：全カラム表示・検索結果5件・デフォルト日付範囲での表示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-022　アコーディオン詳細展開確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：「＋」ボタンクリックで更改後証券番号・更改後保険料・アップセルSTS・落ちSTS・メモの詳細行が展開されることを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-023　フォローコールSTS「未実施」絞込確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：フォローコールSTS=未実施で絞込み、検索結果2件（山田直子・中村浩司）が表示されることを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-024　担当者列 昇順ソート確認（未実施フィルター後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：フォローコール未実施2件の状態で担当者列ヘッダークリック → S001→S002の昇順ソートを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-025　満期年月日列 昇順ソート確認（全件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：日付条件クリア後、満期年月日ヘッダークリック → 2026-03-20から昇順表示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-026　担当者列 昇順ソート確認（全件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：全件表示の状態で担当者列ヘッダークリック → S001（3件）→S002（2件）の昇順ソートを確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>UT-FLOW-027　年換算保険料列 昇順ソート確認（全件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>確認内容：全件表示の状態で年換算保険料ヘッダークリック → ¥45,000から昇順表示を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>テスト実施日：2026/05/29（過去実施）　　環境：ローカルファイル（file://）　　ブラウザ：Chromium (Playwright headless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="430" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
